--- a/latest/BoM/Generic/pedalboard-soundcard-bom.xlsx
+++ b/latest/BoM/Generic/pedalboard-soundcard-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="149">
   <si>
     <t>Row</t>
   </si>
@@ -163,9 +163,6 @@
     <t>LED_0805_2012Metric</t>
   </si>
   <si>
-    <t>~</t>
-  </si>
-  <si>
     <t>1=K 2=A</t>
   </si>
   <si>
@@ -409,7 +406,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.7+1</t>
+    <t>10.0.1-10.0.1~ubuntu25.10.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -1035,7 +1032,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1048,13 +1045,13 @@
     </row>
     <row r="2" spans="1:11">
       <c r="C2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F2" s="3">
         <v>21</v>
@@ -1062,41 +1059,41 @@
     </row>
     <row r="3" spans="1:11">
       <c r="C3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="C4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="C5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1104,13 +1101,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F6" s="3">
         <v>73</v>
@@ -1352,33 +1349,33 @@
         <v>18</v>
       </c>
       <c r="I14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1">
       <c r="A15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>21</v>
@@ -1387,10 +1384,10 @@
         <v>18</v>
       </c>
       <c r="I15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>12</v>
@@ -1404,16 +1401,16 @@
         <v>12</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>11</v>
@@ -1422,10 +1419,10 @@
         <v>18</v>
       </c>
       <c r="I16" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>12</v>
@@ -1439,28 +1436,28 @@
         <v>12</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="G17" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>12</v>
@@ -1468,22 +1465,22 @@
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>17</v>
@@ -1492,10 +1489,10 @@
         <v>18</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>12</v>
@@ -1509,16 +1506,16 @@
         <v>12</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="F19" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>27</v>
@@ -1527,10 +1524,10 @@
         <v>18</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>12</v>
@@ -1538,22 +1535,22 @@
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="F20" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>36</v>
@@ -1562,10 +1559,10 @@
         <v>18</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>12</v>
@@ -1573,22 +1570,22 @@
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>17</v>
@@ -1597,10 +1594,10 @@
         <v>18</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>12</v>
@@ -1608,22 +1605,22 @@
     </row>
     <row r="22" spans="1:11" ht="45" customHeight="1">
       <c r="A22" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>84</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>11</v>
@@ -1632,10 +1629,10 @@
         <v>18</v>
       </c>
       <c r="I22" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>12</v>
@@ -1643,22 +1640,22 @@
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
       <c r="A23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="F23" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>27</v>
@@ -1667,10 +1664,10 @@
         <v>18</v>
       </c>
       <c r="I23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>12</v>
@@ -1678,22 +1675,22 @@
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>11</v>
@@ -1702,10 +1699,10 @@
         <v>18</v>
       </c>
       <c r="I24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J24" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>12</v>
@@ -1713,22 +1710,22 @@
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
       <c r="A25" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>11</v>
@@ -1737,10 +1734,10 @@
         <v>18</v>
       </c>
       <c r="I25" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>12</v>
@@ -1748,22 +1745,22 @@
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="F26" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>112</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>11</v>
@@ -1772,10 +1769,10 @@
         <v>18</v>
       </c>
       <c r="I26" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="K26" s="12" t="s">
         <v>12</v>
@@ -1783,22 +1780,22 @@
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
       <c r="A27" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="F27" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>11</v>
@@ -1807,10 +1804,10 @@
         <v>18</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>12</v>
@@ -1834,7 +1831,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="6" width="40.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
@@ -1845,7 +1842,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1858,13 +1855,13 @@
     </row>
     <row r="2" spans="1:11">
       <c r="C2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F2" s="3">
         <v>21</v>
@@ -1872,41 +1869,41 @@
     </row>
     <row r="3" spans="1:11">
       <c r="C3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="C4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="C5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1914,13 +1911,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F6" s="3">
         <v>73</v>
@@ -1969,28 +1966,28 @@
         <v>12</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>143</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>12</v>
@@ -2004,28 +2001,28 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>12</v>
@@ -2051,27 +2048,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
